--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487429_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487429_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.096299999999999</v>
+        <v>6.9882</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7547</v>
+        <v>5.8337</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3416</v>
+        <v>1.1545</v>
       </c>
       <c r="G2" t="n">
         <v>3.8508</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3619</v>
+        <v>1.2538</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3725</v>
+        <v>1.4515</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0106</v>
+        <v>-0.1978</v>
       </c>
       <c r="V2" t="n">
         <v>1.492</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9835</v>
+        <v>5.002</v>
       </c>
       <c r="E3" t="n">
-        <v>5.631</v>
+        <v>4.4624</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3525</v>
+        <v>0.5396</v>
       </c>
       <c r="G3" t="n">
         <v>4.3947</v>
@@ -688,13 +688,13 @@
         <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8215</v>
+        <v>0.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9567</v>
+        <v>0.7881</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1352</v>
+        <v>0.0519</v>
       </c>
       <c r="V3" t="n">
         <v>0.5507</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.674</v>
+        <v>4.4914</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7159</v>
+        <v>6.1057</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.042</v>
+        <v>-1.6143</v>
       </c>
       <c r="G4" t="n">
         <v>3.2292</v>
@@ -766,13 +766,13 @@
         <v>2.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.614</v>
+        <v>0.2035</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0692</v>
+        <v>0.3205</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5447</v>
+        <v>-0.117</v>
       </c>
       <c r="V4" t="n">
         <v>0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5591</v>
+        <v>1.8382</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2527</v>
+        <v>0.6387</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3064</v>
+        <v>1.1995</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3089</v>
@@ -844,13 +844,13 @@
         <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5132</v>
+        <v>0.7922</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6309</v>
+        <v>1.0169</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1177</v>
+        <v>-0.2247</v>
       </c>
       <c r="V5" t="n">
         <v>1.159</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4855</v>
+        <v>1.3297</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3738</v>
+        <v>1.2715</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1117</v>
+        <v>0.0582</v>
       </c>
       <c r="G6" t="n">
         <v>0.7554</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1426</v>
+        <v>-0.0132</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3258</v>
+        <v>0.2235</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1833</v>
+        <v>-0.2367</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5255</v>
+        <v>0.8117</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4319</v>
+        <v>-0.0655</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9574</v>
+        <v>0.8772</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5633</v>
@@ -1000,13 +1000,13 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5575</v>
+        <v>-0.2713</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5346</v>
+        <v>-0.1682</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0229</v>
+        <v>-0.1031</v>
       </c>
       <c r="V7" t="n">
         <v>0.2754</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3863</v>
+        <v>0.3817</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9001</v>
+        <v>1.0024</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5138</v>
+        <v>-0.6208</v>
       </c>
       <c r="G8" t="n">
         <v>0.22</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1663</v>
+        <v>0.1617</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0594</v>
+        <v>0.0429</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2257</v>
+        <v>0.1188</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. IGOA ENDJILO</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3635</v>
+        <v>0.2773</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2376</v>
+        <v>-0.7794</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1259</v>
+        <v>1.0567</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3396</v>
+        <v>-1.5772</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.476</v>
+        <v>0.7272</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1364</v>
+        <v>-2.3044</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.0501</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.6533</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.7034</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3396</v>
+        <v>-1.5271</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.476</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1364</v>
+        <v>-1.601</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2198</v>
+        <v>0.5423</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2376</v>
+        <v>0.4458</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0178</v>
+        <v>0.0965</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>X. IGOA ENDJILO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4893</v>
+        <v>-0.2344</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7598</v>
+        <v>-0.1353</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2705</v>
+        <v>-0.0992</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5772</v>
+        <v>-0.3396</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7272</v>
+        <v>-0.476</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3044</v>
+        <v>0.1364</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0501</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6533</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7034</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5271</v>
+        <v>-0.3396</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07389999999999999</v>
+        <v>-0.476</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.601</v>
+        <v>0.1364</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2243</v>
+        <v>-0.0907</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5346</v>
+        <v>-0.1353</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3103</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>X. QUINTELA VALCARCEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6591</v>
+        <v>-1.9609</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4889</v>
+        <v>-0.4577</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1481</v>
+        <v>-1.5033</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6355</v>
+        <v>1.5621</v>
       </c>
       <c r="H11" t="n">
-        <v>1.557</v>
+        <v>2.1532</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1924</v>
+        <v>-0.591</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9093</v>
+        <v>3.7704</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8236</v>
+        <v>3.0333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0857</v>
+        <v>0.7371</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5447</v>
+        <v>-2.2083</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2667</v>
+        <v>-0.8801</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2781</v>
+        <v>-1.3281</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7419</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1128</v>
+        <v>-5.0921</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1099</v>
+        <v>0.9066</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.864</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5177</v>
+        <v>0.0426</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6083</v>
+        <v>-1.492</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-1.492</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X. QUINTELA VALCARCEL</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9446</v>
+        <v>-2.3741</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.174</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7706</v>
+        <v>-2.3085</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5621</v>
+        <v>-0.6355</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1532</v>
+        <v>1.557</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.591</v>
+        <v>-2.1924</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7704</v>
+        <v>1.9093</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0333</v>
+        <v>1.8236</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7371</v>
+        <v>0.0857</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2083</v>
+        <v>-2.5447</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8801</v>
+        <v>-0.2667</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3281</v>
+        <v>-2.2781</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.9377</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.0921</v>
+        <v>-4.1128</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1543</v>
+        <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.077</v>
+        <v>0.3949</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1476</v>
+        <v>0.0376</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2247</v>
+        <v>0.3573</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.492</v>
+        <v>0.6083</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X12" t="n">
         <v>-1.492</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.2537</v>
+        <v>16.5508</v>
       </c>
       <c r="E13" t="n">
-        <v>17.5138</v>
+        <v>17.8108</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2603</v>
+        <v>-1.2604</v>
       </c>
       <c r="G13" t="n">
         <v>10.5877</v>
@@ -1438,7 +1438,7 @@
         <v>9.879399999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7080000000000009</v>
+        <v>0.7080000000000011</v>
       </c>
       <c r="J13" t="n">
         <v>25.2592</v>
@@ -1453,10 +1453,10 @@
         <v>-14.6717</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.770499999999999</v>
+        <v>-6.7705</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.9014</v>
+        <v>-7.901399999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-1.958699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>18.6054</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4228</v>
+        <v>4.7198</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5903</v>
+        <v>4.887300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1676</v>
+        <v>-0.1676000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>3.2017</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1461</v>
+        <v>6.2602</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6556</v>
+        <v>7.1439</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5095</v>
+        <v>-0.8837</v>
       </c>
       <c r="G14" t="n">
         <v>3.6896</v>
@@ -1546,13 +1546,13 @@
         <v>3.917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4392</v>
+        <v>-0.4467</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7575</v>
+        <v>0.2458</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3183</v>
+        <v>-0.6925</v>
       </c>
       <c r="V14" t="n">
         <v>0.2754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0562</v>
+        <v>1.5224</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8349</v>
+        <v>2.2209</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.6985</v>
       </c>
       <c r="G15" t="n">
         <v>0.3654</v>
@@ -1624,13 +1624,13 @@
         <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1033</v>
+        <v>0.5695</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1863</v>
+        <v>0.5723</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.083</v>
+        <v>-0.0028</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8043</v>
+        <v>1.0716</v>
       </c>
       <c r="E16" t="n">
         <v>1.2571</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4528</v>
+        <v>-0.1855</v>
       </c>
       <c r="G16" t="n">
         <v>0.7295</v>
@@ -1702,13 +1702,13 @@
         <v>3.1336</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3709</v>
+        <v>-1.1036</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2392</v>
+        <v>-0.9719</v>
       </c>
       <c r="V16" t="n">
         <v>-1.492</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7186</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3559</v>
+        <v>-0.5606</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0746</v>
+        <v>1.2617</v>
       </c>
       <c r="G17" t="n">
         <v>0.9141</v>
@@ -1780,13 +1780,13 @@
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1006</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3852</v>
+        <v>0.1806</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2846</v>
+        <v>-0.0975</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8837</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2879</v>
+        <v>0.2634</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7272</v>
+        <v>0.0915</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4393</v>
+        <v>0.172</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4346</v>
@@ -1858,13 +1858,13 @@
         <v>3.3294</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.439</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9922</v>
+        <v>-0.1735</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0018</v>
+        <v>-0.2655</v>
       </c>
       <c r="V18" t="n">
         <v>0.9412</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3989</v>
+        <v>-1.2386</v>
       </c>
       <c r="E19" t="n">
         <v>-2.2712</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8723</v>
+        <v>1.0327</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7457</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1452</v>
+        <v>-0.9848</v>
       </c>
       <c r="T19" t="n">
         <v>-0.297</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8482</v>
+        <v>-0.6878</v>
       </c>
       <c r="V19" t="n">
         <v>1.492</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.552</v>
+        <v>-2.4497</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="F20" t="n">
         <v>-2.4332</v>
@@ -2014,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2553</v>
+        <v>-0.1529</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U20" t="n">
         <v>-0.1364</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3643</v>
+        <v>-3.1935</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0295</v>
+        <v>0.3044</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3348</v>
+        <v>-3.4979</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2051</v>
+        <v>-1.478</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3664</v>
+        <v>-1.7761</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1613</v>
+        <v>0.2981</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6988</v>
+        <v>1.4354</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9309</v>
+        <v>0.0612</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7679</v>
+        <v>1.3741</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4936</v>
+        <v>-2.9134</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5645</v>
+        <v>-1.8374</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9292</v>
+        <v>-1.076</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7626</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1985</v>
+        <v>-0.1072</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4576</v>
+        <v>-0.1517</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7409</v>
+        <v>0.0446</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4249</v>
+        <v>-3.32</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0997</v>
+        <v>-0.8248</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5246</v>
+        <v>-2.4952</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.478</v>
+        <v>0.2051</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7761</v>
+        <v>0.3664</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2981</v>
+        <v>-0.1613</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4354</v>
+        <v>2.6988</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0612</v>
+        <v>1.9309</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3741</v>
+        <v>0.7679</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9134</v>
+        <v>-2.4936</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8374</v>
+        <v>-1.5645</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.076</v>
+        <v>-0.9292</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3917</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3386</v>
+        <v>-1.1542</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3564</v>
+        <v>-0.2529</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0178</v>
+        <v>-0.9013</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6796</v>
+        <v>-4.4762</v>
       </c>
       <c r="E23" t="n">
-        <v>1.054</v>
+        <v>0.3377</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7336</v>
+        <v>-4.8138</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3001</v>
@@ -2248,13 +2248,13 @@
         <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9546</v>
+        <v>0.1581</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0369</v>
+        <v>0.3205</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0823</v>
+        <v>-0.1625</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5507</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9672</v>
+        <v>-5.6557</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8604</v>
+        <v>-4.6558</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1068</v>
+        <v>-0.9999</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6026</v>
@@ -2326,13 +2326,13 @@
         <v>1.3709</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1066</v>
+        <v>0.4182</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2247</v>
+        <v>0.4293</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1181</v>
+        <v>-0.0112</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8837</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3038</v>
+        <v>-5.7387</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.278</v>
+        <v>-1.7663</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.0259</v>
+        <v>-3.9724</v>
       </c>
       <c r="G25" t="n">
         <v>-3.8501</v>
@@ -2404,13 +2404,13 @@
         <v>2.3502</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8282</v>
+        <v>-1.263</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0692</v>
+        <v>-0.5576</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7589</v>
+        <v>-0.7055</v>
       </c>
       <c r="V25" t="n">
         <v>0.9412</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.2534</v>
+        <v>-16.2537</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2603</v>
+        <v>1.260300000000001</v>
       </c>
       <c r="F26" t="n">
         <v>-17.5137</v>
@@ -2452,7 +2452,7 @@
         <v>-9.8794</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7083000000000004</v>
+        <v>-0.7083000000000008</v>
       </c>
       <c r="J26" t="n">
         <v>14.6718</v>
@@ -2482,10 +2482,10 @@
         <v>20.564</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.422800000000001</v>
+        <v>-4.422499999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1677</v>
+        <v>0.1676</v>
       </c>
       <c r="U26" t="n">
         <v>-4.5903</v>
